--- a/cour/cour formation/RCP101/Td prob stochastique.xlsx
+++ b/cour/cour formation/RCP101/Td prob stochastique.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torrs\Documents\GitHub\Dossier-Projet\cour\cour formation\RCP101\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FE969F3-4A11-4538-A6BF-939ADF869A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7E24A4-FD5F-4120-B738-8FCDB76A3ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{98DD8F82-0120-4C20-A0E4-67084F7C29C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{98DD8F82-0120-4C20-A0E4-67084F7C29C0}"/>
   </bookViews>
   <sheets>
     <sheet name="exercice 1" sheetId="1" r:id="rId1"/>
     <sheet name="exercice 2" sheetId="2" r:id="rId2"/>
     <sheet name="exercice 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Exercice 4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="43">
   <si>
     <t>etat</t>
   </si>
@@ -279,19 +280,51 @@
       <t/>
     </r>
   </si>
+  <si>
+    <t>B : Pluie</t>
+  </si>
+  <si>
+    <t>t0</t>
+  </si>
+  <si>
+    <t>t1</t>
+  </si>
+  <si>
+    <t>t2</t>
+  </si>
+  <si>
+    <t>t3</t>
+  </si>
+  <si>
+    <t>t4</t>
+  </si>
+  <si>
+    <t>t5</t>
+  </si>
+  <si>
+    <t>t6</t>
+  </si>
+  <si>
+    <t>t7</t>
+  </si>
+  <si>
+    <t>t8</t>
+  </si>
+  <si>
+    <t>t9</t>
+  </si>
+  <si>
+    <t>t10</t>
+  </si>
+  <si>
+    <t>A : Beau</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,16 +400,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1870,7 +1913,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1878,13 +1921,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3469D3-3366-4BE0-B3C0-1A310AE89575}">
-  <dimension ref="B2:AF28"/>
+  <dimension ref="B2:Z28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="16384" width="10.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:26" x14ac:dyDescent="0.35">
       <c r="J2" s="1" t="s">
         <v>20</v>
       </c>
@@ -1892,20 +1935,8 @@
         <f>M6*T6*X6</f>
         <v>0</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="6"/>
-      <c r="AF2" s="6"/>
-    </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="6"/>
-    </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1948,13 +1979,8 @@
       <c r="Z4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
-    </row>
-    <row r="5" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:26" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="str">
         <f>C4</f>
         <v>h</v>
@@ -2016,13 +2042,8 @@
       <c r="Z5" s="2">
         <v>1</v>
       </c>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
-    </row>
-    <row r="6" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:26" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="str">
         <f>D4</f>
         <v>a</v>
@@ -2084,13 +2105,8 @@
       <c r="Z6" s="2">
         <v>0.9</v>
       </c>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-    </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="str">
         <f>E4</f>
         <v>f</v>
@@ -2104,41 +2120,8 @@
       <c r="E7" s="2">
         <v>0.9</v>
       </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-    </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-    </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="6"/>
-      <c r="AD9" s="6"/>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-    </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
@@ -2150,7 +2133,7 @@
         <v>1.8000000000000002E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:26" x14ac:dyDescent="0.35">
       <c r="L14" s="3" t="str">
         <f>L4</f>
         <v>h</v>
@@ -2182,7 +2165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:26" ht="16.5" x14ac:dyDescent="0.45">
       <c r="J15" s="3" t="s">
         <v>5</v>
       </c>
@@ -2229,7 +2212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:26" ht="16.5" x14ac:dyDescent="0.45">
       <c r="J16" s="3" t="s">
         <v>7</v>
       </c>
@@ -2278,20 +2261,6 @@
       <c r="Z16" s="2">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="17" spans="10:20" x14ac:dyDescent="0.35">
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="10:20" x14ac:dyDescent="0.35">
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
     </row>
     <row r="21" spans="10:20" x14ac:dyDescent="0.35">
       <c r="J21" s="1" t="s">
@@ -2394,26 +2363,12 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="10:20" x14ac:dyDescent="0.35">
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-    </row>
-    <row r="27" spans="10:20" x14ac:dyDescent="0.35">
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-    </row>
     <row r="28" spans="10:20" x14ac:dyDescent="0.35">
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2422,41 +2377,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE4C3982-8043-42A7-971D-542D425ED48A}">
-  <dimension ref="B2:AF31"/>
+  <dimension ref="B2:P21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="16384" width="10.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="K2" s="4"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="6"/>
-      <c r="AF2" s="6"/>
-    </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="6"/>
-    </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2490,24 +2420,8 @@
       <c r="P4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
-    </row>
-    <row r="5" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
@@ -2550,24 +2464,8 @@
       <c r="P5" s="2">
         <v>0</v>
       </c>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
-    </row>
-    <row r="6" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
@@ -2610,24 +2508,8 @@
       <c r="P6" s="2">
         <v>0.5</v>
       </c>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-    </row>
-    <row r="7" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="2:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
@@ -2648,7 +2530,6 @@
         <f>1/2</f>
         <v>0.5</v>
       </c>
-      <c r="I7" s="6"/>
       <c r="J7" s="3" t="s">
         <v>8</v>
       </c>
@@ -2662,7 +2543,7 @@
       <c r="M7" s="2">
         <v>0.29166666666666663</v>
       </c>
-      <c r="N7" s="8">
+      <c r="N7" s="5">
         <v>0.29166666666666663</v>
       </c>
       <c r="O7" s="2">
@@ -2671,24 +2552,8 @@
       <c r="P7" s="2">
         <v>0.16666666666666666</v>
       </c>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-    </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
@@ -2707,32 +2572,8 @@
       <c r="G8" s="2">
         <v>1</v>
       </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-    </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
@@ -2755,26 +2596,8 @@
       <c r="G9" s="2">
         <v>0</v>
       </c>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="6"/>
-      <c r="AD9" s="6"/>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-    </row>
-    <row r="10" spans="2:32" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
       <c r="L10" s="3" t="s">
         <v>24</v>
       </c>
@@ -2790,20 +2613,8 @@
       <c r="P10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
-      <c r="AB10" s="6"/>
-    </row>
-    <row r="11" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="2:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="J11" s="3" t="s">
         <v>5</v>
       </c>
@@ -2825,20 +2636,8 @@
       <c r="P11" s="2">
         <v>0</v>
       </c>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="6"/>
-      <c r="AB11" s="6"/>
-    </row>
-    <row r="12" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="2:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="J12" s="3" t="s">
         <v>7</v>
       </c>
@@ -2861,20 +2660,8 @@
       <c r="P12" s="2">
         <v>1</v>
       </c>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="6"/>
-      <c r="AB12" s="6"/>
-    </row>
-    <row r="13" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="2:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="J13" s="3" t="s">
         <v>8</v>
       </c>
@@ -2897,20 +2684,8 @@
       <c r="P13" s="2">
         <v>0</v>
       </c>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="6"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="6"/>
-      <c r="AB13" s="6"/>
-    </row>
-    <row r="14" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="14" spans="2:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="J14" s="3" t="s">
         <v>9</v>
       </c>
@@ -2933,20 +2708,8 @@
       <c r="P14" s="2">
         <v>0.58333333333333326</v>
       </c>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="6"/>
-      <c r="AB14" s="6"/>
-    </row>
-    <row r="15" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="15" spans="2:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="J15" s="3" t="s">
         <v>10</v>
       </c>
@@ -2969,20 +2732,8 @@
       <c r="P15" s="2">
         <v>0.16666666666666666</v>
       </c>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
-      <c r="AB15" s="6"/>
-    </row>
-    <row r="16" spans="2:32" ht="16.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="16" spans="2:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="J16" s="3" t="s">
         <v>11</v>
       </c>
@@ -2996,7 +2747,7 @@
       <c r="M16" s="2">
         <v>0.11805555555555552</v>
       </c>
-      <c r="N16" s="8">
+      <c r="N16" s="5">
         <v>0.11805555555555552</v>
       </c>
       <c r="O16" s="2">
@@ -3005,321 +2756,467 @@
       <c r="P16" s="2">
         <v>0.45138888888888878</v>
       </c>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="6"/>
-      <c r="AA16" s="6"/>
-      <c r="AB16" s="6"/>
-    </row>
-    <row r="17" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6"/>
-      <c r="T17" s="6"/>
-      <c r="U17" s="6"/>
-      <c r="V17" s="6"/>
-      <c r="W17" s="6"/>
-      <c r="X17" s="6"/>
-      <c r="Y17" s="6"/>
-      <c r="Z17" s="6"/>
-      <c r="AA17" s="6"/>
-      <c r="AB17" s="6"/>
-    </row>
-    <row r="18" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6"/>
-      <c r="AB18" s="6"/>
-    </row>
-    <row r="19" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
-      <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="6"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="6"/>
-      <c r="AA19" s="6"/>
-      <c r="AB19" s="6"/>
-    </row>
-    <row r="20" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="W20" s="6"/>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="6"/>
-      <c r="Z20" s="6"/>
-      <c r="AA20" s="6"/>
-      <c r="AB20" s="6"/>
-    </row>
-    <row r="21" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J21" s="6"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="6"/>
-      <c r="T21" s="6"/>
-      <c r="U21" s="6"/>
-      <c r="V21" s="6"/>
-      <c r="W21" s="6"/>
-      <c r="X21" s="6"/>
-      <c r="Y21" s="6"/>
-      <c r="Z21" s="6"/>
-      <c r="AA21" s="6"/>
-      <c r="AB21" s="6"/>
-    </row>
-    <row r="22" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="6"/>
-      <c r="W22" s="6"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6"/>
-      <c r="Z22" s="6"/>
-      <c r="AA22" s="6"/>
-      <c r="AB22" s="6"/>
-    </row>
-    <row r="23" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="6"/>
-      <c r="T23" s="6"/>
-      <c r="U23" s="6"/>
-      <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="6"/>
-      <c r="AB23" s="6"/>
-    </row>
-    <row r="24" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="6"/>
-      <c r="AB24" s="6"/>
-    </row>
-    <row r="25" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6"/>
-      <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
-      <c r="V25" s="6"/>
-      <c r="W25" s="6"/>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="6"/>
-      <c r="AB25" s="6"/>
-    </row>
-    <row r="26" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="6"/>
-      <c r="T26" s="6"/>
-      <c r="U26" s="6"/>
-      <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
-      <c r="X26" s="6"/>
-      <c r="Y26" s="6"/>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="6"/>
-      <c r="AB26" s="6"/>
-    </row>
-    <row r="27" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="6"/>
-      <c r="Y27" s="6"/>
-      <c r="Z27" s="6"/>
-      <c r="AA27" s="6"/>
-      <c r="AB27" s="6"/>
-    </row>
-    <row r="28" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="6"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="6"/>
-      <c r="AB28" s="6"/>
-    </row>
-    <row r="29" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6"/>
-      <c r="T29" s="6"/>
-      <c r="U29" s="6"/>
-      <c r="V29" s="6"/>
-      <c r="W29" s="6"/>
-      <c r="X29" s="6"/>
-      <c r="Y29" s="6"/>
-      <c r="Z29" s="6"/>
-      <c r="AA29" s="6"/>
-      <c r="AB29" s="6"/>
-    </row>
-    <row r="30" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6"/>
-      <c r="W30" s="6"/>
-      <c r="X30" s="6"/>
-      <c r="Y30" s="6"/>
-      <c r="Z30" s="6"/>
-      <c r="AA30" s="6"/>
-      <c r="AB30" s="6"/>
-    </row>
-    <row r="31" spans="10:28" x14ac:dyDescent="0.35">
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="6"/>
-      <c r="S31" s="6"/>
-      <c r="T31" s="6"/>
-      <c r="U31" s="6"/>
-      <c r="V31" s="6"/>
-      <c r="W31" s="6"/>
-      <c r="X31" s="6"/>
-      <c r="Y31" s="6"/>
-      <c r="Z31" s="6"/>
-      <c r="AA31" s="6"/>
-      <c r="AB31" s="6"/>
+    </row>
+    <row r="21" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K21" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3492EA7-F869-4CBB-8521-89D327C5173C}">
+  <dimension ref="A2:W24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="16384" width="10.90625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="1" cm="1">
+        <f t="array" ref="I5:J5">MMULT(I4:J4,$D$4:$E$5)</f>
+        <v>0.3</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="1" cm="1">
+        <f t="array" ref="I6:J6">MMULT(I5:J5,$D$4:$E$5)</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.54999999999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="1" cm="1">
+        <f t="array" ref="I7:J7">MMULT(I6:J6,$D$4:$E$5)</f>
+        <v>0.52499999999999991</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.47499999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="1" cm="1">
+        <f t="array" ref="I8:J8">MMULT(I7:J7,$D$4:$E$5)</f>
+        <v>0.56249999999999989</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.43749999999999994</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="H9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="1" cm="1">
+        <f t="array" ref="I9:J9">MMULT(I8:J8,$D$4:$E$5)</f>
+        <v>0.58124999999999993</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.41874999999999996</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="H10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="1" cm="1">
+        <f t="array" ref="I10:J10">MMULT(I9:J9,$D$4:$E$5)</f>
+        <v>0.59062499999999996</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.40937499999999993</v>
+      </c>
+      <c r="K10" s="9"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="H11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="1" cm="1">
+        <f t="array" ref="I11:J11">MMULT(I10:J10,$D$4:$E$5)</f>
+        <v>0.59531249999999991</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.40468749999999992</v>
+      </c>
+      <c r="K11" s="8"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="H12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="1" cm="1">
+        <f t="array" ref="I12:J12">MMULT(I11:J11,$D$4:$E$5)</f>
+        <v>0.59765624999999989</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.40234374999999989</v>
+      </c>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="H13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" s="1" cm="1">
+        <f t="array" ref="I13:J13">MMULT(I12:J12,$D$4:$E$5)</f>
+        <v>0.59882812499999982</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.4011718749999999</v>
+      </c>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="H14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="1" cm="1">
+        <f t="array" ref="I14:J14">MMULT(I13:J13,$D$4:$E$5)</f>
+        <v>0.59941406249999984</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.40058593749999988</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+    </row>
+    <row r="17" spans="10:23" x14ac:dyDescent="0.35">
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+    </row>
+    <row r="18" spans="10:23" x14ac:dyDescent="0.35">
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+    </row>
+    <row r="19" spans="10:23" x14ac:dyDescent="0.35">
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+    </row>
+    <row r="20" spans="10:23" x14ac:dyDescent="0.35">
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+      <c r="V20" s="8"/>
+      <c r="W20" s="8"/>
+    </row>
+    <row r="21" spans="10:23" x14ac:dyDescent="0.35">
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="8"/>
+    </row>
+    <row r="22" spans="10:23" x14ac:dyDescent="0.35">
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+    </row>
+    <row r="23" spans="10:23" x14ac:dyDescent="0.35">
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="8"/>
+      <c r="V23" s="8"/>
+      <c r="W23" s="8"/>
+    </row>
+    <row r="24" spans="10:23" x14ac:dyDescent="0.35">
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="8"/>
+      <c r="W24" s="8"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>